--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -581,16 +581,16 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -655,12 +655,12 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -729,38 +729,38 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-26, 2026-03-30</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-03-04, 2026-03-10, 2026-03-18, 2026-03-25, 2026-03-30</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-23</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-23, 2026-03-30</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-10, 2026-02-17, 2026-02-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>1</v>
+        <v>0.8</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="5">
@@ -819,12 +819,12 @@
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -833,30 +833,18 @@
       <c r="P5" t="n">
         <v>4</v>
       </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>2026-02-04, 2026-02-11</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
       <c r="T5" t="inlineStr"/>
       <c r="U5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -905,12 +893,12 @@
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -921,35 +909,35 @@
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-25, 2026-02-26</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-09, 2026-02-16, 2026-02-21, 2026-02-25</t>
+          <t>2026-03-02, 2026-03-06, 2026-03-16, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-12, 2026-02-19, 2026-02-26</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-02-20</t>
+          <t>2026-03-06, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.25</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -995,12 +983,12 @@
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -1069,19 +1057,19 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="P2" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P3" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P4" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8</v>
+        <v>0.4</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.4444444444444444</v>
       </c>
     </row>
     <row r="5">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P5" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P6" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="X6" t="n">
-        <v>0.75</v>
+        <v>0.375</v>
       </c>
     </row>
     <row r="7">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="P7" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5</v>
+        <v>9</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -590,10 +590,10 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="P2" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr"/>
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="O3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P3" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
@@ -738,10 +738,10 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P4" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
@@ -770,10 +770,10 @@
         <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>0.4</v>
+        <v>0.8</v>
       </c>
       <c r="X4" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
     <row r="5">
@@ -828,10 +828,10 @@
         </is>
       </c>
       <c r="O5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr"/>
@@ -902,10 +902,10 @@
         </is>
       </c>
       <c r="O6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P6" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
@@ -934,10 +934,10 @@
         <v>3</v>
       </c>
       <c r="W6" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.375</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
@@ -992,10 +992,10 @@
         </is>
       </c>
       <c r="O7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P7" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
@@ -1066,10 +1066,10 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="P8" t="n">
-        <v>9</v>
+        <v>4.5</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr"/>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -546,7 +546,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>BELLATERRA AREIA</t>
+          <t>BELATERRA AREIA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -595,21 +595,37 @@
       <c r="P2" t="n">
         <v>4</v>
       </c>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-10, 2026-03-18, 2026-03-24, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -620,7 +636,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>BELLATERRA PIETRA</t>
+          <t>BELATERRA PIETRA</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -669,21 +685,37 @@
       <c r="P3" t="n">
         <v>4</v>
       </c>
-      <c r="Q3" t="inlineStr"/>
-      <c r="R3" t="inlineStr"/>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-20</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
+        </is>
+      </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="4">
@@ -948,7 +980,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>BELLATERRA TEMPUS</t>
+          <t>BELATERRA TEMPUS</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -997,21 +1029,37 @@
       <c r="P7" t="n">
         <v>4</v>
       </c>
-      <c r="Q7" t="inlineStr"/>
-      <c r="R7" t="inlineStr"/>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-12, 2026-03-19, 2026-03-21, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-07, 2026-03-12, 2026-03-20, 2026-03-21, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-20, 2026-03-26</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-20, 2026-03-21, 2026-03-27</t>
+        </is>
+      </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -1071,21 +1119,37 @@
       <c r="P8" t="n">
         <v>4.5</v>
       </c>
-      <c r="Q8" t="inlineStr"/>
-      <c r="R8" t="inlineStr"/>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-23</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.6</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>0.8888888888888888</v>
       </c>
     </row>
   </sheetData>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -985,7 +985,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t xml:space="preserve">Ejecución </t>
+          <t>Ejecución</t>
         </is>
       </c>
       <c r="D7" t="inlineStr"/>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -787,7 +787,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-23, 2026-03-30</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-23, 2026-03-24, 2026-03-30</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -796,13 +796,13 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="V4" t="n">
         <v>4</v>
       </c>
       <c r="W4" t="n">
-        <v>0.8</v>
+        <v>1</v>
       </c>
       <c r="X4" t="n">
         <v>0.8888888888888888</v>
@@ -956,20 +956,20 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>0.75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -761,7 +761,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-23, 2026-03-24, 2026-03-30</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-25, 2026-03-30</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -796,7 +796,7 @@
         </is>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="V4" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-17, 2026-03-18, 2026-03-23, 2026-03-24, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-23</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -1140,13 +1140,13 @@
         </is>
       </c>
       <c r="U8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V8" t="n">
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="X8" t="n">
         <v>0.8888888888888888</v>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -581,7 +581,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
@@ -590,7 +590,7 @@
         </is>
       </c>
       <c r="O2" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
         <v>4</v>
@@ -622,7 +622,7 @@
         <v>4</v>
       </c>
       <c r="W2" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
       <c r="X2" t="n">
         <v>1</v>
@@ -761,42 +761,42 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="O4" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="P4" t="n">
+        <v>4</v>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-26, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>2026-03-04, 2026-03-10, 2026-03-18, 2026-03-25, 2026-03-30</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-25</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="U4" t="n">
         <v>5</v>
-      </c>
-      <c r="P4" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-26, 2026-03-30</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-10, 2026-03-18, 2026-03-25, 2026-03-30</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-25, 2026-03-30</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
-        </is>
-      </c>
-      <c r="U4" t="n">
-        <v>6</v>
       </c>
       <c r="V4" t="n">
         <v>4</v>
@@ -805,7 +805,7 @@
         <v>1</v>
       </c>
       <c r="X4" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -1105,19 +1105,19 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-30, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-31</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="O8" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="P8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
@@ -1146,10 +1146,10 @@
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="X8" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -761,7 +761,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -770,7 +770,7 @@
         </is>
       </c>
       <c r="O4" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P4" t="n">
         <v>4</v>
@@ -1105,7 +1105,7 @@
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25, 2026-03-31</t>
+          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="O8" t="n">
-        <v>4.5</v>
+        <v>4</v>
       </c>
       <c r="P8" t="n">
         <v>4</v>
@@ -1146,7 +1146,7 @@
         <v>4</v>
       </c>
       <c r="W8" t="n">
-        <v>0.8888888888888888</v>
+        <v>1</v>
       </c>
       <c r="X8" t="n">
         <v>1</v>

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -607,12 +607,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -697,12 +697,12 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -787,16 +787,16 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U4" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V4" t="n">
         <v>4</v>
@@ -951,12 +951,12 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-14, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1041,25 +1041,25 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-20, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-20, 2026-03-21, 2026-03-27</t>
+          <t>2026-03-07, 2026-03-21, 2026-03-28</t>
         </is>
       </c>
       <c r="U7" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="V7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W7" t="n">
         <v>1</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="8">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-24</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U8" t="n">

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -607,12 +607,12 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-10, 2026-03-18, 2026-03-24</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U2" t="n">
@@ -697,12 +697,12 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
+          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-20</t>
         </is>
       </c>
       <c r="U3" t="n">
@@ -787,12 +787,12 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
+          <t>2026-03-04, 2026-03-10, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U4" t="n">
@@ -951,12 +951,12 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-05, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-14, 2026-03-21, 2026-03-28</t>
+          <t>2026-03-06, 2026-03-16, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="U6" t="n">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-13, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-12, 2026-03-19, 2026-03-26</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-21, 2026-03-28</t>
+          <t>2026-03-07, 2026-03-20, 2026-03-28</t>
         </is>
       </c>
       <c r="U7" t="n">
@@ -1131,12 +1131,12 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
+          <t>2026-03-02, 2026-03-09, 2026-03-16, 2026-03-24</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>2026-03-03, 2026-03-10, 2026-03-17, 2026-03-25</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2026-03-04, 2026-03-11, 2026-03-18, 2026-03-25</t>
         </is>
       </c>
       <c r="U8" t="n">

--- a/output/resumen.xlsx
+++ b/output/resumen.xlsx
@@ -956,20 +956,20 @@
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-16, 2026-03-20, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-20, 2026-03-27</t>
         </is>
       </c>
       <c r="U6" t="n">
         <v>4</v>
       </c>
       <c r="V6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="W6" t="n">
         <v>1</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="7">
